--- a/GameDesign/Storage/SampleData/CommonConfig.xlsx
+++ b/GameDesign/Storage/SampleData/CommonConfig.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2882C3F-9ED3-41BA-AEA5-01154243E121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBCA2C6-8AFC-4F3F-977E-0BD43208C5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>basic_having_envergy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>후공 플레이어 첫 턴 에너지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>max_unit_size_to_field</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>min_deck_card_count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,6 +112,14 @@
   </si>
   <si>
     <t>선택 대기 시간 (ms초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basic_having_energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_field_unit_count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,7 +474,7 @@
   <dimension ref="A2:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -518,95 +518,95 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>60000</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>2000</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/CommonConfig.xlsx
+++ b/GameDesign/Storage/SampleData/CommonConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBCA2C6-8AFC-4F3F-977E-0BD43208C5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460DEF4F-A941-4D29-B4E9-4906E0CD8369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,6 +120,14 @@
   </si>
   <si>
     <t>max_field_unit_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gain_prize_by_direct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상대방 플레이어 직접공격을 통해 얻는 프라이즈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -197,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}" name="CommonConfig" displayName="CommonConfig" ref="A2:C13" totalsRowShown="0">
-  <autoFilter ref="A2:C13" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}" name="CommonConfig" displayName="CommonConfig" ref="A2:C14" totalsRowShown="0">
+  <autoFilter ref="A2:C14" xr:uid="{E2719ABB-62B7-41DC-8FF6-A3988B691283}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1EFB0E40-FCB9-4E2B-931E-5C2FE6377C40}" name="Name"/>
     <tableColumn id="2" xr3:uid="{D87CD009-B99B-43FB-902E-215BEE534F1B}" name="Value"/>
@@ -471,12 +479,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C13"/>
+  <dimension ref="A2:C14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -607,6 +615,17 @@
       </c>
       <c r="C13" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/CommonConfig.xlsx
+++ b/GameDesign/Storage/SampleData/CommonConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460DEF4F-A941-4D29-B4E9-4906E0CD8369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34691D3E-A6E4-4015-BF51-BD0236EDC411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CommonConfig" sheetId="1" r:id="rId1"/>

--- a/GameDesign/Storage/SampleData/CommonConfig.xlsx
+++ b/GameDesign/Storage/SampleData/CommonConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34691D3E-A6E4-4015-BF51-BD0236EDC411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0B7C43-245B-4C9E-A881-E5723E122AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,7 +600,7 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -611,7 +611,7 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
